--- a/tiflow/TMD-3168-architekturbild-ti-flow-fachdienst-finalisieren/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/TMD-3168-architekturbild-ti-flow-fachdienst-finalisieren/2.0.0-ballot.2/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:48:27+00:00</t>
+    <t>2026-06-18T05:39:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
